--- a/artfynd/A 6477-2024 artfynd.xlsx
+++ b/artfynd/A 6477-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954666</v>
       </c>
       <c r="B2" t="n">
-        <v>110324</v>
+        <v>110330</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6477-2024 artfynd.xlsx
+++ b/artfynd/A 6477-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954666</v>
       </c>
       <c r="B2" t="n">
-        <v>110330</v>
+        <v>110332</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6477-2024 artfynd.xlsx
+++ b/artfynd/A 6477-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954666</v>
       </c>
       <c r="B2" t="n">
-        <v>110332</v>
+        <v>110333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6477-2024 artfynd.xlsx
+++ b/artfynd/A 6477-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954666</v>
       </c>
       <c r="B2" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6477-2024 artfynd.xlsx
+++ b/artfynd/A 6477-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954666</v>
       </c>
       <c r="B2" t="n">
-        <v>110339</v>
+        <v>110343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6477-2024 artfynd.xlsx
+++ b/artfynd/A 6477-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954666</v>
       </c>
       <c r="B2" t="n">
-        <v>110343</v>
+        <v>110345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6477-2024 artfynd.xlsx
+++ b/artfynd/A 6477-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954666</v>
       </c>
       <c r="B2" t="n">
-        <v>110345</v>
+        <v>110347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6477-2024 artfynd.xlsx
+++ b/artfynd/A 6477-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954666</v>
       </c>
       <c r="B2" t="n">
-        <v>110347</v>
+        <v>110360</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6477-2024 artfynd.xlsx
+++ b/artfynd/A 6477-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954666</v>
       </c>
       <c r="B2" t="n">
-        <v>110360</v>
+        <v>110362</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6477-2024 artfynd.xlsx
+++ b/artfynd/A 6477-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954666</v>
       </c>
       <c r="B2" t="n">
-        <v>110362</v>
+        <v>110367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6477-2024 artfynd.xlsx
+++ b/artfynd/A 6477-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954666</v>
       </c>
       <c r="B2" t="n">
-        <v>110367</v>
+        <v>110389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6477-2024 artfynd.xlsx
+++ b/artfynd/A 6477-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954666</v>
       </c>
       <c r="B2" t="n">
-        <v>110389</v>
+        <v>110390</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6477-2024 artfynd.xlsx
+++ b/artfynd/A 6477-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954666</v>
       </c>
       <c r="B2" t="n">
-        <v>110390</v>
+        <v>110395</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6477-2024 artfynd.xlsx
+++ b/artfynd/A 6477-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954666</v>
       </c>
       <c r="B2" t="n">
-        <v>110395</v>
+        <v>110398</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6477-2024 artfynd.xlsx
+++ b/artfynd/A 6477-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954666</v>
       </c>
       <c r="B2" t="n">
-        <v>110398</v>
+        <v>110404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6477-2024 artfynd.xlsx
+++ b/artfynd/A 6477-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954666</v>
       </c>
       <c r="B2" t="n">
-        <v>110404</v>
+        <v>110405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6477-2024 artfynd.xlsx
+++ b/artfynd/A 6477-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954666</v>
       </c>
       <c r="B2" t="n">
-        <v>110405</v>
+        <v>110417</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6477-2024 artfynd.xlsx
+++ b/artfynd/A 6477-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954666</v>
       </c>
       <c r="B2" t="n">
-        <v>110417</v>
+        <v>110418</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6477-2024 artfynd.xlsx
+++ b/artfynd/A 6477-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954666</v>
       </c>
       <c r="B2" t="n">
-        <v>110418</v>
+        <v>110421</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6477-2024 artfynd.xlsx
+++ b/artfynd/A 6477-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954666</v>
       </c>
       <c r="B2" t="n">
-        <v>110421</v>
+        <v>110423</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6477-2024 artfynd.xlsx
+++ b/artfynd/A 6477-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954666</v>
       </c>
       <c r="B2" t="n">
-        <v>110423</v>
+        <v>110427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
